--- a/muldrow_tables.xlsx
+++ b/muldrow_tables.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Table 7 — Logistic Regression" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Table 8 — Multinomial Regressio" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Table 9 — Robustness Checks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Other Category Breakdown" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -112,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -157,6 +158,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1704,13 +1715,2986 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Appendix: Cases Coded as 'Other' in Primary Basis for Dismissal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Summary: What comprises the 'Other' category</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Original Value</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>% of Period Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>(blank — no dismissal basis recorded)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>27.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Multiple Bases</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Procedural / Forfeiture</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>(blank — no dismissal basis recorded)</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>6.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Total Pre: 11 (8.5%)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Total Post: 75 (29.3%)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="21" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Case-Level Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Case Name</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Circuit</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Decision Date</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Court Finding on Harm</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Original Primary Basis for Dismissal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Blount v. St. Louis County Department of Public Health</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>8/11/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>EEOC v. Northwest Arkansas Hospitals, LLC</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>5/28/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Johnson v. Kansas City Public Schools</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>6/27/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Lamai v. Central Iowa Hospital Corporation</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>9/24/2024</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Madumelu v. Collins Aerospace</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>2/3/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Procedural / Forfeiture</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>McLeod v. Southeast Community College Area</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>3/24/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Pankonin v. Southeast Community College Area</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>7/9/2025</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Pinner v. American Association of Orthodontists</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>9/19/2024</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Pujji v. Buttigieg</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>1/29/2025</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Smith v. Tapley</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>9/19/2025</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>Procedural / Forfeiture</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Wilder v. Honeywell Federal Manufacturing &amp; Technologies, LLC</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>10/24/2024</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Albert v. Fidelity Brokerage Services LLC</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>11/19/2025</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Bennett v. Butler County Board of Education</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>1/3/2025</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Bethel v. United Parcel Service, Inc.</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>8/27/2025</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Cole v. Young</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>12/26/2024</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Procedural / Forfeiture</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Freeman v. Jupiter Inlet Colony</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>4/7/2025</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Lowry v. Hwaseung Automotive USA, LLC</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>9/13/2024</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Martinez-Lopez v. GFA Alabama Inc.</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>8/28/2025</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Nolan v. St. Johns County School Board</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>9/3/2024</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Reynolds v. Johnson Controls, Inc.</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>11/5/2025</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Rucker v. Belcher</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>3/20/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Sutherland v. City of Pembroke Pines</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>10/15/2025</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Tolliver v. City of Birmingham</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>3/25/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Walker v. Baptist Health System, Inc.</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Wood v. Florida Department of Education</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>7/10/2024</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Zhang v. Board of Regents of the University System of Georgia</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Eleventh</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>8/26/2024</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Harrison v. Berry</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>5/14/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Makalou v. ABCD &amp; Company, LLC</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>3/6/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>McPherson v. Employment Source, Inc.</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>3/31/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Noble v. Toshiba Global Commerce Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>3/25/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Prescott v. At Management, LLC</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>4/30/2025</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Price v. Durham Public Schools</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>2/18/2025</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Rageh v. University of North Carolina at Chapel Hill</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>12/10/2024</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Rios-Grajales v. Bondi</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>8/28/2025</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Smallwood v. Mayor and City Council of Baltimore: Baltimore Police Department</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>2/13/2025</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Thomas v. Montgomery County, Maryland</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>7/21/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Tribue v. Maryland</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>9/13/2024</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Watson v. Wake County Public School System</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>8/26/2025</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Zanders v. Lutnick</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Fourth</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>4/28/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Agapov v. UBIF Franchising Co.</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>12/16/2024</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Carter v. City of Hartford</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>3/26/2025</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Dipiano v. New York City Department of Education</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>9/14/2025</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Fagan v. Mount Vernon City School District</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>3/27/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Gilmore v. Saratoga Center for Care, LLC</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>1/8/2025</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Guerrero v. Constellation Health Services, LLC</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>9/4/2025</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Hinds v. PSEG Long Island LLC</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>2/2/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Jones v. International Association of Sheet Metal, Air, Rail and Transportation Workers</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>7/25/2025</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>Moy v. Napoli Shkolnik, PLLC</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>7/22/2024</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Noh v. Admarketplace, Inc.</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>3/28/2025</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>Ong v. Deloitte Consulting, LLP</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>3/21/2025</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Sabic-El-Rayess v. Teachers College, Columbia University</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>12/5/2024</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>Schoenadel v. YouGov America Inc.</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>2/3/2025</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Wilson v. Yonkers Public Schools</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>9/19/2025</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>Chesnut v. Chicago Public Schools</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>Seventh</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>11/26/2024</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Galvan v. City of Chicago</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Seventh</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>4/8/2026</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>Hoffman v. Board of Regents of the University of Wisconsin System</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>Seventh</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>5/27/2025</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Jones v. McHenry County</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Seventh</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>10/4/2024</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>Miller v. O'Malley</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>Seventh</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>9/19/2024</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Morris v. City of Chicago</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Seventh</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>6/23/2026</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>Russell v. Village of Skokie</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>Seventh</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>5/23/2025</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Benton v. Honeywell International Inc.</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>3/11/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>Berry v. Garland</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>1/9/2025</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>Procedural / Forfeiture</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Broil v. Kansas Bureau of Investigation</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>3/26/2025</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>Eguakun v. Gusto, Inc.</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>5/15/2024</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>Multiple Bases</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Eguakun v. Gusto, Inc.</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>12/6/2024</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>Multiple Bases</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Green v. Oklahoma Gas &amp; Electric Co.</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>3/12/2025</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Howard v. Kansas Wesleyan University</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>9/17/2025</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>Juarez v. Midwest Division – OPRMC, LLC</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>11/5/2024</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>King v. Koch AG &amp; Energy Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>7/28/2025</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>King v. Koch AG &amp; Energy Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>4/20/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Miller v. Prudential Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>5/1/2025</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>Mills v. Amazon.com Services, LLC</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>6/27/2024</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>Revan v. University of Denver Department of Campus Safety</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>2/11/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>Reynolds v. United Parcel Service, Inc.</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>10/28/2025</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Ybarra v. Board of County Commissioners</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>3/31/2026</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>Nahum v. LMI Aerospace, Inc.</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>Eighth</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>6/28/2021</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>Oquendo v. Costco Wholesale Corp.</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>4/7/2020</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Dinis v. New York DOE</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>2/8/2024</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>Jennings v. City of New York</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>1/26/2023</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Kurtanidze v. Mizuho Bank, Ltd</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>3/13/2024</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>Insufficient</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>Lall v. City of New York</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>3/5/2021</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>McDowell v. McDonough</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>12/21/2022</t>
+        </is>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>Miliean v. NYC DOE</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>9/15/2023</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Supino v. Suny Downstate Medical Center</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>3/15/2021</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>Valerio v. City of New York</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>1/21/2020</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Plain v. Nichols Management, Inc.</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Tenth</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>Pre</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>5/10/2022</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>Sufficient</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>(blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Note: 'Other' in the analysis comprises: original 'Other' (2 pre-period cases), Procedural/Forfeiture (4 post), Multiple Bases (2 post), and cases with no Primary Basis recorded. Missing Primary Basis most commonly occurs when Court Finding on Harm = 'Not Reached' or plaintiff survived (N/A — Plaintiff Survived). Recommend reviewing blank cases to confirm they are correctly excluded from dismissal basis analysis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2012,6 +4996,101 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Note: χ² tests use Pearson chi-square without continuity correction.  * p&lt;0.05  ** p&lt;0.01  *** p&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Non-Economic Adverse Action Claim Outcome</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dismissed — Plaintiff</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>119</v>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>91.5%</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>173</v>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>67.6%</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>0.000***</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mixed</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Survived — Plaintiff</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Note: χ² tests use Pearson chi-square without continuity correction.  * p&lt;0.05  ** p&lt;0.01  *** p&lt;0.001</t>
         </is>
@@ -2031,27 +5110,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 3. Outcome by Period and Filing Date Subgroup</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="35" customHeight="1">
+          <t>Table 3. Outcome by Period and Filing Date Subgroup (Corrected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Outcome</t>
@@ -2070,8 +5149,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Post — Pre-Muldrow Filing
-N=168</t>
+          <t>Post — Pre-Muldrow
+Filing (N=168)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2081,8 +5160,8 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Post — Post-Muldrow Filing
-N=88</t>
+          <t>Post — Post-Muldrow
+Filing (N=88)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2092,8 +5171,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>χ²  p-value
-(3-way)</t>
+          <t>χ²  p-value (3-way)</t>
         </is>
       </c>
     </row>
@@ -2112,136 +5190,136 @@
       <c r="H3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Insufficient</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>73.8%</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="15" t="n">
         <v>61</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>36.3%</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>0.000***</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sufficient</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>10.8%</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="17" t="n">
         <v>61</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>36.3%</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="17" t="n">
         <v>42</v>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mixed</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>13.1%</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>11.3%</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>13.6%</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="H6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Not Reached</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>16.1%</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>13.6%</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2258,173 +5336,287 @@
       <c r="H8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Harm Insufficient</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>70.0%</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="15" t="n">
         <v>59</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>35.1%</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>23.9%</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>0.000***</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Causation Insufficient</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>16.9%</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="17" t="n">
         <v>67</v>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>39.9%</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>29.5%</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  N/A — Plaintiff Survived</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>1.5%</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>2.4%</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>4.5%</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
+      <c r="H11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pleading Deficiency</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>3.1%</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Other</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>8.5%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>22.6%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>42.0%</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Note: χ² test is across all three groups.  * p&lt;0.05  ** p&lt;0.01  *** p&lt;0.001</t>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Non-Economic Adverse Action Claim Outcome</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dismissed — Plaintiff</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>119</v>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>91.5%</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>74.4%</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>0.000***</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mixed</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Survived — Plaintiff</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>22.0%</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Note: Post — Pre-Muldrow Filing = cases decided post-Muldrow but filed before 4/17/2024 (N=168, includes 1 case with missing filing date). Post — Post-Muldrow Filing = filed on or after 4/17/2024 (N=88). χ² tests are across all three groups.  * p&lt;0.05  ** p&lt;0.01  *** p&lt;0.001</t>
         </is>
       </c>
     </row>
@@ -3451,7 +6643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5023,20 +8215,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table 8. Multinomial Logistic Regression: Primary Basis for Dismissal</t>
+          <t>Table 8. Binary Logistic Regression: Causation Insufficient vs. Harm Insufficient</t>
         </is>
       </c>
     </row>
@@ -5048,7 +8240,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Relative Risk Ratio</t>
+          <t>Odds Ratio</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5063,14 +8255,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Outcome: Causation Insufficient (vs. Harm Insufficient)</t>
+          <t>Outcome: 1 = Causation Insufficient, 0 = Harm Insufficient  (N=260, McFadden R²=0.109)  Excludes: Other, N/A — Survived, Pleading Deficiency</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -5086,24 +8278,20 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>1.260</t>
+          <t>0.160</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.044, 0.587]</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>0.763</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.006**</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -5113,24 +8301,20 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1.440</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.423, 4.900]</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>0.827</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.559</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -5140,24 +8324,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>0.958</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.050, 18.198]</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>0.969</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.977</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -5167,24 +8347,20 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1.311</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.423, 4.067]</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>0.913</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.639</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -5194,24 +8370,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>1.490</t>
+          <t>1.141</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.382, 3.407]</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>0.531</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.813</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -5221,24 +8393,20 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.417, 4.681]</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>0.755</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.588</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -5248,213 +8416,181 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.243, 3.371]</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>0.572</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.882</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>C(Motion_Type_Decided)[T.12(c) Judgment on Pleadings]</t>
+          <t>C(Employer_Type)[T.Government - Municipal]</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>1.050</t>
+          <t>1.117</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.483, 2.585]</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>0.986</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.795</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>C(Motion_Type_Decided)[T.Other]</t>
+          <t>C(Employer_Type)[T.Government - State]</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>1.884</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.635, 5.594]</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>0.840</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.254</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>C(Motion_Type_Decided)[T.Summary Judgment]</t>
+          <t>C(Employer_Type)[T.Private]</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>0.891</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.410, 1.937]</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>0.884</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.770</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>C(Employer_Type)[T.Government - Municipal]</t>
+          <t>C(Appointing_President_Party)[T.Republican]</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>0.842</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.465, 1.527]</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>0.999</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.572</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>C(Employer_Type)[T.Government - State]</t>
+          <t>C(Motion_Type_Decided)[T.12(c) Judgment on Pleadings]</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.000, 532822405379719887430565025898691033434404191872116601180206848618713141609811055499860010287914487721371995097316737466276609200344587300551892162572881309596236776004795403247014176075546868793376390584845126164545536.000]</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>0.869</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.967</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>C(Employer_Type)[T.Private]</t>
+          <t>C(Motion_Type_Decided)[T.Other]</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.000, 62677270188022899173000932742915497330865395033403053071741289540309068454856552015277195747506108072757606323119544135106108139602886331069104263320090863909034054397493437923440163761387992833655682987052274044610909702270382262653895934214144.000]</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>0.910</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.970</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>C(Appointing_President_Party)[T.Republican]</t>
+          <t>C(Motion_Type_Decided)[T.Summary Judgment]</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>1.206</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[0.790, 2.719]</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>0.595</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.226</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -5464,1277 +8600,25 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>4.719</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[2.542, 8.762]</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>0.206</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>Causation Insufficient</t>
-        </is>
-      </c>
+          <t>0.000***</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Outcome: N/A — Plaintiff Survived (vs. Harm Insufficient)</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>0.915</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>0.926</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Eleventh]</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>0.939</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>0.946</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.First]</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>1.260</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>0.886</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Fourth]</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>0.887</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>0.885</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Second]</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>0.650</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>0.598</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Seventh]</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>1.118</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Tenth]</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>1.013</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>0.990</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.12(c) Judgment on Pleadings]</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>1.176</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>0.964</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.Other]</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>0.969</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>0.987</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.Summary Judgment]</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>0.874</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>0.785</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Government - Municipal]</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>1.084</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>0.903</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Government - State]</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>0.984</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>0.986</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Private]</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>1.150</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>0.824</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>C(Appointing_President_Party)[T.Republican]</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>0.979</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>0.963</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>0.819</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>N/A — Plaintiff Survived</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Outcome: Pleading Deficiency (vs. Harm Insufficient)</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>0.610</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>0.712</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Eleventh]</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>0.940</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.First]</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>1.104</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>0.964</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Fourth]</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>0.905</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>0.934</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Second]</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>1.008</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>0.994</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Seventh]</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>1.672</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Tenth]</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>1.010</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>0.994</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.12(c) Judgment on Pleadings]</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>1.156</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>0.976</t>
-        </is>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.Other]</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>1.078</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>0.976</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.Summary Judgment]</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>0.481</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>0.245</t>
-        </is>
-      </c>
-      <c r="E45" s="17" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Government - Municipal]</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>0.934</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>0.936</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Government - State]</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>1.163</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="inlineStr">
-        <is>
-          <t>0.894</t>
-        </is>
-      </c>
-      <c r="E47" s="17" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Private]</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>0.886</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>0.882</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>C(Appointing_President_Party)[T.Republican]</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>0.710</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>0.585</t>
-        </is>
-      </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>0.822</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>Pleading Deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Outcome: Other (vs. Harm Insufficient)</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>0.889</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>0.905</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Eleventh]</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>0.912</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>0.928</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.First]</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>0.945</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>0.976</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Fourth]</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>1.269</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>0.783</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Second]</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>1.047</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>0.957</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Seventh]</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>0.937</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>0.946</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>C(Circuit)[T.Tenth]</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>1.211</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>0.855</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.12(c) Judgment on Pleadings]</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>0.945</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>0.988</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.Other]</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>0.962</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>0.985</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>C(Motion_Type_Decided)[T.Summary Judgment]</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>0.816</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>0.674</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Government - Municipal]</t>
-        </is>
-      </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>0.994</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>0.992</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Government - State]</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>1.026</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>0.977</t>
-        </is>
-      </c>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>C(Employer_Type)[T.Private]</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t>0.894</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>0.857</t>
-        </is>
-      </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>C(Appointing_President_Party)[T.Republican]</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>0.877</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>0.779</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>0.833</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>0.691</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>Note: Ref outcome=Harm Insufficient. N=280. Simplified spec: period, circuit, motion type, employer type, appointing party. Note: Hessian non-invertible — p-values from Nelder-Mead, CIs unavailable; treat with caution.  * p&lt;0.05  ** p&lt;0.01  *** p&lt;0.001</t>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Note: Binary logit — outcome = 1 if primary dismissal basis is Causation / Discriminatory Intent Insufficient, 0 if Harm Insufficient. Cases with Other, N/A — Plaintiff Survived, or Pleading Deficiency excluded. N=260 (102 causation, 158 harm insuff). Reference categories: Circuit=Eighth, Employer=Gov-Federal, Party=Democrat, Motion=12(b)(6). Adverse action type omitted (not significant in Table 7 spec).  * p&lt;0.05  ** p&lt;0.01  *** p&lt;0.001</t>
         </is>
       </c>
     </row>

--- a/muldrow_tables.xlsx
+++ b/muldrow_tables.xlsx
@@ -1570,17 +1570,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>87 (22.5%)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>11 (8.5%)</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>76 (29.7%)</t>
         </is>
       </c>
     </row>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>93 (24.1%)</t>
+          <t>6 (1.6%)</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>13 (10.0%)</t>
+          <t>2 (1.5%)</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>80 (31.2%)</t>
+          <t>4 (1.6%)</t>
         </is>
       </c>
     </row>
@@ -1884,19 +1884,19 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
@@ -1932,19 +1932,19 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -2271,27 +2271,27 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
@@ -2335,27 +2335,27 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr"/>
@@ -5361,12 +5361,12 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
